--- a/reports/tables/comparativa_svm.xlsx
+++ b/reports/tables/comparativa_svm.xlsx
@@ -571,22 +571,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7637</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>0.5255</v>
+        <v>0.7347</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>0.6892</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.1525</v>
+        <v>0.1809</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5853</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.5538</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>0.8</v>
+        <v>0.5918</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.7939000000000001</v>
       </c>
     </row>
   </sheetData>
